--- a/data/sprints_db.xlsx
+++ b/data/sprints_db.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,140 +485,40 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>testes</t>
+          <t>Matheus Gabriel</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t xml:space="preserve">- Documentação do sistema e da estrutura do banco de dados													
+- Check sobre MarketingCloud													
+- Criação DashTI(centralização de andamento de projeto, calendario, sprint e chamados)													
+- MeLembre concluido por aqui		
+- Adicionar dados DashTI e deploy												
+</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t xml:space="preserve">Atualização do backend autoserviço													
+</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>teste</t>
+          <t xml:space="preserve">- Finalização de projeto DashTi e já utilização													
+- Backend Atualizado													
+</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>teste</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>46090</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Governança &amp; Sustentação</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>teste</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>teste</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>teste</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>teste</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>teste</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>46090</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Governança &amp; Sustentação</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>rwarw</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ataet</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>teat</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>teaet</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>teate</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>46090</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Estratégia &amp; Projetos</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>taeat</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>teate</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>teat</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>aeae</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>tatee</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>atete</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
     </row>
